--- a/Soluciones en Excel/VaR de bonos.xlsx
+++ b/Soluciones en Excel/VaR de bonos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/106876cc2438bd37/Desktop/TRABAJO/UNI/8VO SEMESTRE/ADMINISTRACION_RIESGOS/Soluciones en Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF362D71-67D4-4534-A456-BDB537B6A3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DF362D71-67D4-4534-A456-BDB537B6A3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{129DD36D-8CCB-4667-8164-ABA97BB04212}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A56D5B87-D6BE-4DAC-8CE3-7DC73E4687D9}"/>
   </bookViews>

--- a/Soluciones en Excel/VaR de bonos.xlsx
+++ b/Soluciones en Excel/VaR de bonos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/106876cc2438bd37/Desktop/TRABAJO/UNI/8VO SEMESTRE/ADMINISTRACION_RIESGOS/Soluciones en Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Desktop\TRABAJO\UNI\8VO SEMESTRE\ADMINISTRACION_RIESGOS\Soluciones en Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DF362D71-67D4-4534-A456-BDB537B6A3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{129DD36D-8CCB-4667-8164-ABA97BB04212}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6938116-9C68-403B-9ED4-C36115F2F088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A56D5B87-D6BE-4DAC-8CE3-7DC73E4687D9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A56D5B87-D6BE-4DAC-8CE3-7DC73E4687D9}"/>
   </bookViews>
   <sheets>
     <sheet name="indicaciones" sheetId="1" r:id="rId1"/>
@@ -599,21 +599,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C4F68F3-85FC-41B5-BC57-4FF5CE7AC89F}">
   <dimension ref="B1:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C1" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>13</v>
       </c>
@@ -636,7 +636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -661,7 +661,7 @@
         <v>0.76946593784069606</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -686,12 +686,12 @@
         <v>-0.23053406215930394</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F7" t="s">
         <v>18</v>
       </c>
@@ -702,7 +702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="E8" s="2">
         <v>46814</v>
       </c>
@@ -718,7 +718,7 @@
         <v>62638.679200028782</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="E9" s="2">
         <v>49726</v>
       </c>
@@ -734,27 +734,27 @@
         <v>67373.412300004056</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C12" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C13" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" s="11" t="s">
         <v>31</v>
       </c>
@@ -770,20 +770,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55DA484E-7399-4093-8F70-0C9AAFC747D0}">
   <dimension ref="A1:M262"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,7 +821,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>46063</v>
       </c>
@@ -872,7 +872,7 @@
         <v>-538987.29840003292</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>46062</v>
       </c>
@@ -916,7 +916,7 @@
         <v>-57903.946100052272</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>46059</v>
       </c>
@@ -960,7 +960,7 @@
         <v>356893.14280026313</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>46058</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>-293167.31469989277</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>46057</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>394771.0076000829</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>46056</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>4734.733099969606</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>46055</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>46052</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>332132.32840004348</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>46051</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>-538987.29840003292</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>46050</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>178446.57140013756</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>46049</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>-23673.665499882249</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>46048</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>139481.55769999238</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>46045</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>173711.83830015038</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>46044</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>-302636.7808998375</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>46043</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>-374744.92629982729</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>46042</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>307371.51399982464</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>46041</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>-67373.412300002616</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>46038</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>105251.27709980484</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>46037</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>206854.96999998303</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>46036</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>120542.62530008529</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>46035</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>192650.7707000575</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>46034</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>125277.35840006046</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>46031</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>404240.47380002768</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>46030</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>81577.611599934549</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>46029</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>-462144.41990008549</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>46028</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>-37877.864799802192</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>46027</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>-33143.131699827092</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>46024</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>115807.89220011013</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>46023</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>-278963.11539997277</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>46022</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>46021</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>-144216.29079995002</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>46020</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>62638.679200027444</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>46017</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>139481.55769998039</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>46016</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>46015</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>-178446.57140013756</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>46014</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>-264758.91610004083</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>46013</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>427914.13929989794</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>46010</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>46009</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>178446.57140013756</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>46008</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>231615.78440022026</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>46007</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>361627.87590023829</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>46006</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>336867.06150002504</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>46003</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>46002</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>-255289.44990008496</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>46001</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>-192650.77070006309</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46000</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>13117.050399565138</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>45999</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>-29495.547500200395</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>45996</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>14204.199299937492</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>45995</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>-57903.946100057845</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>45994</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>-2148654.0252008848</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>45993</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>-86312.344699897745</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>45992</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>144216.29079995002</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>45989</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>202120.23690001984</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>45988</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>-76842.878499959377</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>45987</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>-100516.54399982968</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>45986</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>57903.946100052272</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>45985</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>45982</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>148951.02389993714</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>45981</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>134746.82460000523</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>45980</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>134746.82460000523</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>45979</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>-134746.82460000523</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>45978</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>45975</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>67373.412300002616</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>45974</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>-67373.412300002616</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>45973</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>-211589.70309996459</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>45972</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>9469.4661999567616</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>45971</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>9469.4661999503442</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>45968</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>-38965.013700162701</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>45967</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>-250554.71680011536</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>45966</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>9469.4661999623349</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>45965</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>-120542.62530008529</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>45964</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>-57903.946100052272</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>45961</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>-134746.82460000523</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>45960</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>515313.63290015061</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>45959</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>235263.36859983497</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>45958</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>-529517.83220007061</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>45957</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>125277.35840005489</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>45954</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>206854.96999998303</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>45953</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>274228.38229999761</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>45952</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>245819.98370012821</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>45951</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>-717433.86980015854</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>45950</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>515313.63290015061</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>45947</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>404240.47380002768</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>45946</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>115807.89220011013</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>45945</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>-211589.70309997015</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>45944</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>-250554.71680011536</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>45943</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>125277.35840006046</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>45940</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>366362.60900022549</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>45939</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>-538987.29840003292</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>45938</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>654795.19060014305</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>45937</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>202120.23690000785</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>45936</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>-192650.77070006309</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>45933</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>202120.23690000785</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>45932</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>-125277.35840005489</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>45931</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>635856.2582002359</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>45930</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>-144216.29079995558</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>45929</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>9469.4661999503442</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>45926</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>-53169.213000082673</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>45925</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>72108.145399989779</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>45924</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>264758.91610003531</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>45923</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>-264758.91610003531</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>45922</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>192650.7707000575</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>45919</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>274228.38229998568</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>45918</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>-28408.398599845474</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>45917</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>-264758.9161000473</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>45916</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>45915</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>520048.36600013782</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>45912</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>332132.32840003789</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>45911</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>-418444.67309994763</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>45910</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>-216324.43619993978</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>45909</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>134746.82460001722</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>45908</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>-18938.932399907091</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>45905</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>96868.95980020304</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>45904</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>-148951.02389993076</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>45903</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>-245819.98370014018</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>45902</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>313193.39600014279</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>45901</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>45898</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>134746.82460000523</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>45897</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>-9469.4661999447708</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>45896</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>-260024.18300006568</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>45895</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>-67373.412300002616</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>45894</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>260024.18300006568</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>45891</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>-451587.80479978025</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>45890</v>
       </c>
@@ -6284,7 +6284,7 @@
         <v>-236350.51750018986</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>45889</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>317928.12910011795</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>45888</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>-206854.96999998303</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>45887</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>202120.23690000785</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>45884</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>14204.199299931934</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>45883</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>206854.96999998303</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>45882</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>-404240.47380002768</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>45881</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>-14204.199299919943</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>45880</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>115807.89220011013</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>45877</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>86312.344699897745</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>45876</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>101603.6929001846</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>45875</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>38965.013700150768</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>45874</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>524783.09910010733</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>45873</v>
       </c>
@@ -6856,7 +6856,7 @@
         <v>-264758.9161000473</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>45870</v>
       </c>
@@ -6900,7 +6900,7 @@
         <v>-706877.25469986536</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>45869</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>-4734.7330999751721</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>45868</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>-4734.7330999751721</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>45867</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>-351071.26079993945</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>45866</v>
       </c>
@@ -7076,7 +7076,7 @@
         <v>235263.36859983497</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>45863</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>255289.44990009692</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>45862</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>452674.95370012877</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>45861</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>-9469.4661999503442</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>45860</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>1477480.3375001063</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>45859</v>
       </c>
@@ -7296,7 +7296,7 @@
         <v>-260024.18300006012</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>45856</v>
       </c>
@@ -7340,7 +7340,7 @@
         <v>413709.93999996688</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>45855</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>264758.91610004642</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>45854</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>-4734.7330999751721</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>45853</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>202120.23690000785</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>45852</v>
       </c>
@@ -7516,7 +7516,7 @@
         <v>-317928.12910012354</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>45849</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>144216.29079996757</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>45848</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>577952.31210018368</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>45847</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>-336867.06150001311</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>45846</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>332132.32840003789</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>45845</v>
       </c>
@@ -7736,7 +7736,7 @@
         <v>394771.00760007731</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>45842</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>153685.75699990592</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>45841</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>278963.11539996165</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>45840</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>48434.479900113074</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>45839</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>-125277.35840005489</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>45838</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>-548456.76459999522</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>45835</v>
       </c>
@@ -8000,7 +8000,7 @@
         <v>28408.398599851876</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>45834</v>
       </c>
@@ -8044,7 +8044,7 @@
         <v>125277.35840005489</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>45833</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>-14204.199299914384</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>45832</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>-760046.46769995335</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>45831</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>-543722.03150000807</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>45828</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>163155.22319986823</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>45827</v>
       </c>
@@ -8264,7 +8264,7 @@
         <v>130012.09150003006</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>45826</v>
       </c>
@@ -8308,7 +8308,7 @@
         <v>125277.35840005489</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>45825</v>
       </c>
@@ -8352,7 +8352,7 @@
         <v>211589.70309997015</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>45824</v>
       </c>
@@ -8396,7 +8396,7 @@
         <v>-712699.13670020085</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>45821</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>-67373.412300002616</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>45820</v>
       </c>
@@ -8484,7 +8484,7 @@
         <v>438470.75440020324</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>45819</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>67373.412300002616</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>45818</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>-62638.679200027444</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>45817</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>-443205.48750017839</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>45814</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>-457409.6868001048</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>45813</v>
       </c>
@@ -8704,7 +8704,7 @@
         <v>-4734.7330999751721</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>45812</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>-495287.55159990612</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>45811</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>48434.479900101083</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>45810</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>-125277.35840005489</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>45807</v>
       </c>
@@ -8880,7 +8880,7 @@
         <v>4734.7330999760161</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>45806</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>-33143.131699827092</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>45805</v>
       </c>
@@ -8968,7 +8968,7 @@
         <v>255289.44990009608</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>45804</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>-481083.3522999807</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>45803</v>
       </c>
@@ -9056,7 +9056,7 @@
         <v>-187916.03760008235</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>45800</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>67373.412300002616</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>45799</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>48434.479900101927</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>45798</v>
       </c>
@@ -9188,7 +9188,7 @@
         <v>394771.00760006532</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>45797</v>
       </c>
@@ -9232,7 +9232,7 @@
         <v>-187916.03760008235</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>45796</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>115807.89220010454</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>45793</v>
       </c>
@@ -9320,7 +9320,7 @@
         <v>57903.946100063404</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>45792</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>347423.67660031276</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>45791</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>109986.01019978011</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>45790</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>-178446.57140014315</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>45789</v>
       </c>
@@ -9496,7 +9496,7 @@
         <v>-375832.07520016469</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>45786</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>722168.6029001401</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>45785</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>-361627.87590023829</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>45784</v>
       </c>
@@ -9628,7 +9628,7 @@
         <v>380566.80830015102</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>45783</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>-283697.84849994798</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>45782</v>
       </c>
@@ -9716,7 +9716,7 @@
         <v>134746.82460000523</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>45779</v>
       </c>
@@ -9760,7 +9760,7 @@
         <v>18938.932399912679</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>45778</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>45777</v>
       </c>
@@ -9848,7 +9848,7 @@
         <v>-274228.38229999761</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>45776</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>45775</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>-38965.013700150768</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>45772</v>
       </c>
@@ -9980,7 +9980,7 @@
         <v>-211589.70309997015</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>45771</v>
       </c>
@@ -10024,7 +10024,7 @@
         <v>-625299.64309993712</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>45770</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>-274228.38229998568</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>45769</v>
       </c>
@@ -10112,7 +10112,7 @@
         <v>-471613.88610003033</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>45768</v>
       </c>
@@ -10156,7 +10156,7 @@
         <v>933758.30600009824</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>45765</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>45764</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>45763</v>
       </c>
@@ -10288,7 +10288,7 @@
         <v>120542.62530007973</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>45762</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>298989.19670022291</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>45761</v>
       </c>
@@ -10376,7 +10376,7 @@
         <v>-1501154.002999983</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>45758</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>611095.44380001072</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>45757</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>683203.58919997734</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>45756</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>-394771.00760006532</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>45755</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>538987.29840003292</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>45754</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>1789586.5845999066</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>45751</v>
       </c>
@@ -10640,7 +10640,7 @@
         <v>1087444.0630000161</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>45750</v>
       </c>
@@ -10684,7 +10684,7 @@
         <v>-46260.182099404046</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>45749</v>
       </c>
@@ -10728,7 +10728,7 @@
         <v>-202120.23690000785</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>45748</v>
       </c>
@@ -10772,7 +10772,7 @@
         <v>-105251.27709980484</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>45747</v>
       </c>
@@ -10816,7 +10816,7 @@
         <v>-125277.35840005489</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>45744</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>-576865.16319983511</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>45743</v>
       </c>
@@ -10904,7 +10904,7 @@
         <v>294254.46360024763</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>45742</v>
       </c>
@@ -10948,7 +10948,7 @@
         <v>-187916.03760009346</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>45741</v>
       </c>
@@ -10992,7 +10992,7 @@
         <v>-327397.59530007472</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>45740</v>
       </c>
@@ -11036,7 +11036,7 @@
         <v>-120542.62530007973</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>45737</v>
       </c>
@@ -11080,7 +11080,7 @@
         <v>611095.44380002259</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>45736</v>
       </c>
@@ -11124,7 +11124,7 @@
         <v>139481.55769996927</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>45735</v>
       </c>
@@ -11168,7 +11168,7 @@
         <v>-33143.131699827092</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>45734</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>-14204.199299914384</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>45733</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>45730</v>
       </c>
@@ -11300,7 +11300,7 @@
         <v>-9469.4661999623349</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>45729</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>-423179.40619992843</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>45728</v>
       </c>
@@ -11388,7 +11388,7 @@
         <v>187916.03760009346</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>45727</v>
       </c>
@@ -11432,7 +11432,7 @@
         <v>592156.51140011009</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>45726</v>
       </c>
@@ -11476,7 +11476,7 @@
         <v>471613.88610003033</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>45723</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>62638.679200027444</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>45722</v>
       </c>
@@ -11564,7 +11564,7 @@
         <v>-202120.23690001984</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>45721</v>
       </c>
@@ -11608,7 +11608,7 @@
         <v>-239998.10169981001</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>45720</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>562660.96389992069</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>45719</v>
       </c>
@@ -11696,7 +11696,7 @@
         <v>-197385.5038000558</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>45716</v>
       </c>
@@ -11740,7 +11740,7 @@
         <v>-144216.29079994443</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>45715</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>-260024.18300007127</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>45714</v>
       </c>
@@ -11828,7 +11828,7 @@
         <v>-543722.03149999701</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>45713</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>-47347.330999764497</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>45712</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>-278963.11539996078</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>45709</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>-553191.49769997038</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>45708</v>
       </c>
@@ -12004,7 +12004,7 @@
         <v>-14204.199299914384</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>45707</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>780072.54900019243</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>45706</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>-14204.199299926375</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>45705</v>
       </c>
@@ -12136,7 +12136,7 @@
         <v>264758.9161000473</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>45702</v>
       </c>
@@ -12180,7 +12180,7 @@
         <v>245819.98370014576</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>45701</v>
       </c>
@@ -12224,7 +12224,7 @@
         <v>168977.10520016967</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>45700</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>28408.398599862994</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>45699</v>
       </c>
@@ -12314,16 +12314,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32C00C74-2EFF-44C7-830E-2F9C29BE9767}">
   <dimension ref="A1:I262"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12352,7 +12352,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>46063</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>-935706.55668511696</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>46062</v>
       </c>
@@ -12419,7 +12419,7 @@
       </c>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>46059</v>
       </c>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="I4" s="9"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>46058</v>
       </c>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>46057</v>
       </c>
@@ -12515,7 +12515,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>46056</v>
       </c>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>46055</v>
       </c>
@@ -12579,7 +12579,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>46052</v>
       </c>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>46051</v>
       </c>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>46050</v>
       </c>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>46049</v>
       </c>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>46048</v>
       </c>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>46045</v>
       </c>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>46044</v>
       </c>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>46043</v>
       </c>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>46042</v>
       </c>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>46041</v>
       </c>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>46038</v>
       </c>
@@ -12931,7 +12931,7 @@
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>46037</v>
       </c>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>46036</v>
       </c>
@@ -12995,7 +12995,7 @@
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>46035</v>
       </c>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>46034</v>
       </c>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>46031</v>
       </c>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>46030</v>
       </c>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>46029</v>
       </c>
@@ -13155,7 +13155,7 @@
       </c>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>46028</v>
       </c>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>46027</v>
       </c>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>46024</v>
       </c>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="I29" s="9"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>46023</v>
       </c>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>46022</v>
       </c>
@@ -13315,7 +13315,7 @@
       </c>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>46021</v>
       </c>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>46020</v>
       </c>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>46017</v>
       </c>
@@ -13411,7 +13411,7 @@
       </c>
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>46016</v>
       </c>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>46015</v>
       </c>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>46014</v>
       </c>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>46013</v>
       </c>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>46010</v>
       </c>
@@ -13571,7 +13571,7 @@
       </c>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>46009</v>
       </c>
@@ -13603,7 +13603,7 @@
       </c>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>46008</v>
       </c>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>46007</v>
       </c>
@@ -13667,7 +13667,7 @@
       </c>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>46006</v>
       </c>
@@ -13699,7 +13699,7 @@
       </c>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>46003</v>
       </c>
@@ -13731,7 +13731,7 @@
       </c>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>46002</v>
       </c>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>46001</v>
       </c>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46000</v>
       </c>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="I47" s="9"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>45999</v>
       </c>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="I48" s="9"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>45996</v>
       </c>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="I49" s="9"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>45995</v>
       </c>
@@ -13923,7 +13923,7 @@
       </c>
       <c r="I50" s="9"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>45994</v>
       </c>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="I51" s="9"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>45993</v>
       </c>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>45992</v>
       </c>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>45989</v>
       </c>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="I54" s="9"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>45988</v>
       </c>
@@ -14083,7 +14083,7 @@
       </c>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>45987</v>
       </c>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="I56" s="9"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>45986</v>
       </c>
@@ -14147,7 +14147,7 @@
       </c>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>45985</v>
       </c>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>45982</v>
       </c>
@@ -14211,7 +14211,7 @@
       </c>
       <c r="I59" s="9"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>45981</v>
       </c>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="I60" s="9"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>45980</v>
       </c>
@@ -14275,7 +14275,7 @@
       </c>
       <c r="I61" s="9"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>45979</v>
       </c>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="I62" s="9"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>45978</v>
       </c>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="I63" s="9"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>45975</v>
       </c>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="I64" s="9"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>45974</v>
       </c>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>45973</v>
       </c>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>45972</v>
       </c>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="I67" s="9"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>45971</v>
       </c>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="I68" s="9"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>45968</v>
       </c>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>45967</v>
       </c>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="I70" s="9"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>45966</v>
       </c>
@@ -14595,7 +14595,7 @@
       </c>
       <c r="I71" s="9"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>45965</v>
       </c>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="I72" s="9"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>45964</v>
       </c>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="I73" s="9"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>45961</v>
       </c>
@@ -14691,7 +14691,7 @@
       </c>
       <c r="I74" s="9"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>45960</v>
       </c>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>45959</v>
       </c>
@@ -14755,7 +14755,7 @@
       </c>
       <c r="I76" s="9"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>45958</v>
       </c>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>45957</v>
       </c>
@@ -14819,7 +14819,7 @@
       </c>
       <c r="I78" s="9"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>45954</v>
       </c>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>45953</v>
       </c>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>45952</v>
       </c>
@@ -14915,7 +14915,7 @@
       </c>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>45951</v>
       </c>
@@ -14947,7 +14947,7 @@
       </c>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>45950</v>
       </c>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="I83" s="9"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>45947</v>
       </c>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="I84" s="9"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>45946</v>
       </c>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>45945</v>
       </c>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="I86" s="9"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>45944</v>
       </c>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="I87" s="9"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>45943</v>
       </c>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="I88" s="9"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>45940</v>
       </c>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="I89" s="9"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>45939</v>
       </c>
@@ -15203,7 +15203,7 @@
       </c>
       <c r="I90" s="9"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>45938</v>
       </c>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="I91" s="9"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>45937</v>
       </c>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I92" s="9"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>45936</v>
       </c>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="I93" s="9"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>45933</v>
       </c>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="I94" s="9"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>45932</v>
       </c>
@@ -15363,7 +15363,7 @@
       </c>
       <c r="I95" s="9"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>45931</v>
       </c>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="I96" s="9"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>45930</v>
       </c>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>45929</v>
       </c>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="I98" s="9"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>45926</v>
       </c>
@@ -15491,7 +15491,7 @@
       </c>
       <c r="I99" s="9"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>45925</v>
       </c>
@@ -15523,7 +15523,7 @@
       </c>
       <c r="I100" s="9"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>45924</v>
       </c>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="I101" s="9"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>45923</v>
       </c>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="I102" s="9"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>45922</v>
       </c>
@@ -15619,7 +15619,7 @@
       </c>
       <c r="I103" s="9"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>45919</v>
       </c>
@@ -15651,7 +15651,7 @@
       </c>
       <c r="I104" s="9"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>45918</v>
       </c>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="I105" s="9"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>45917</v>
       </c>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="I106" s="9"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>45916</v>
       </c>
@@ -15747,7 +15747,7 @@
       </c>
       <c r="I107" s="9"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>45915</v>
       </c>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="I108" s="9"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>45912</v>
       </c>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="I109" s="9"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>45911</v>
       </c>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="I110" s="9"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>45910</v>
       </c>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="I111" s="9"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>45909</v>
       </c>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="I112" s="9"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>45908</v>
       </c>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="I113" s="9"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>45905</v>
       </c>
@@ -15971,7 +15971,7 @@
       </c>
       <c r="I114" s="9"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>45904</v>
       </c>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="I115" s="9"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>45903</v>
       </c>
@@ -16035,7 +16035,7 @@
       </c>
       <c r="I116" s="9"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>45902</v>
       </c>
@@ -16067,7 +16067,7 @@
       </c>
       <c r="I117" s="9"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>45901</v>
       </c>
@@ -16099,7 +16099,7 @@
       </c>
       <c r="I118" s="9"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>45898</v>
       </c>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="I119" s="9"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>45897</v>
       </c>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="I120" s="9"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>45896</v>
       </c>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="I121" s="9"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>45895</v>
       </c>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="I122" s="9"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>45894</v>
       </c>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="I123" s="9"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>45891</v>
       </c>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="I124" s="9"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>45890</v>
       </c>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="I125" s="9"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>45889</v>
       </c>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="I126" s="9"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>45888</v>
       </c>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="I127" s="9"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>45887</v>
       </c>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="I128" s="9"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>45884</v>
       </c>
@@ -16451,7 +16451,7 @@
       </c>
       <c r="I129" s="9"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>45883</v>
       </c>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="I130" s="9"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>45882</v>
       </c>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="I131" s="9"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>45881</v>
       </c>
@@ -16547,7 +16547,7 @@
       </c>
       <c r="I132" s="9"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>45880</v>
       </c>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="I133" s="9"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>45877</v>
       </c>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="I134" s="9"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>45876</v>
       </c>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="I135" s="9"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>45875</v>
       </c>
@@ -16675,7 +16675,7 @@
       </c>
       <c r="I136" s="9"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>45874</v>
       </c>
@@ -16707,7 +16707,7 @@
       </c>
       <c r="I137" s="9"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>45873</v>
       </c>
@@ -16739,7 +16739,7 @@
       </c>
       <c r="I138" s="9"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>45870</v>
       </c>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="I139" s="9"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>45869</v>
       </c>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="I140" s="9"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>45868</v>
       </c>
@@ -16835,7 +16835,7 @@
       </c>
       <c r="I141" s="9"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>45867</v>
       </c>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="I142" s="9"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>45866</v>
       </c>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="I143" s="9"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>45863</v>
       </c>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="I144" s="9"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>45862</v>
       </c>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="I145" s="9"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>45861</v>
       </c>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="I146" s="9"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>45860</v>
       </c>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="I147" s="9"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>45859</v>
       </c>
@@ -17059,7 +17059,7 @@
       </c>
       <c r="I148" s="9"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>45856</v>
       </c>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="I149" s="9"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>45855</v>
       </c>
@@ -17123,7 +17123,7 @@
       </c>
       <c r="I150" s="9"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>45854</v>
       </c>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="I151" s="9"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>45853</v>
       </c>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="I152" s="9"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>45852</v>
       </c>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="I153" s="9"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>45849</v>
       </c>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="I154" s="9"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>45848</v>
       </c>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="I155" s="9"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>45847</v>
       </c>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="I156" s="9"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>45846</v>
       </c>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="I157" s="9"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>45845</v>
       </c>
@@ -17379,7 +17379,7 @@
       </c>
       <c r="I158" s="9"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>45842</v>
       </c>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="I159" s="9"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>45841</v>
       </c>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="I160" s="9"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>45840</v>
       </c>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="I161" s="9"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>45839</v>
       </c>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="I162" s="9"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>45838</v>
       </c>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="I163" s="9"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>45835</v>
       </c>
@@ -17571,7 +17571,7 @@
       </c>
       <c r="I164" s="9"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>45834</v>
       </c>
@@ -17603,7 +17603,7 @@
       </c>
       <c r="I165" s="9"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>45833</v>
       </c>
@@ -17635,7 +17635,7 @@
       </c>
       <c r="I166" s="9"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>45832</v>
       </c>
@@ -17667,7 +17667,7 @@
       </c>
       <c r="I167" s="9"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>45831</v>
       </c>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="I168" s="9"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>45828</v>
       </c>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="I169" s="9"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>45827</v>
       </c>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="I170" s="9"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>45826</v>
       </c>
@@ -17795,7 +17795,7 @@
       </c>
       <c r="I171" s="9"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>45825</v>
       </c>
@@ -17827,7 +17827,7 @@
       </c>
       <c r="I172" s="9"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>45824</v>
       </c>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="I173" s="9"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>45821</v>
       </c>
@@ -17891,7 +17891,7 @@
       </c>
       <c r="I174" s="9"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>45820</v>
       </c>
@@ -17923,7 +17923,7 @@
       </c>
       <c r="I175" s="9"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>45819</v>
       </c>
@@ -17955,7 +17955,7 @@
       </c>
       <c r="I176" s="9"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>45818</v>
       </c>
@@ -17987,7 +17987,7 @@
       </c>
       <c r="I177" s="9"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>45817</v>
       </c>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="I178" s="9"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>45814</v>
       </c>
@@ -18051,7 +18051,7 @@
       </c>
       <c r="I179" s="9"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>45813</v>
       </c>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="I180" s="9"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>45812</v>
       </c>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="I181" s="9"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>45811</v>
       </c>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="I182" s="9"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>45810</v>
       </c>
@@ -18179,7 +18179,7 @@
       </c>
       <c r="I183" s="9"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>45807</v>
       </c>
@@ -18211,7 +18211,7 @@
       </c>
       <c r="I184" s="9"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>45806</v>
       </c>
@@ -18243,7 +18243,7 @@
       </c>
       <c r="I185" s="9"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>45805</v>
       </c>
@@ -18275,7 +18275,7 @@
       </c>
       <c r="I186" s="9"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>45804</v>
       </c>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="I187" s="9"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>45803</v>
       </c>
@@ -18339,7 +18339,7 @@
       </c>
       <c r="I188" s="9"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>45800</v>
       </c>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="I189" s="9"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>45799</v>
       </c>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="I190" s="9"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>45798</v>
       </c>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="I191" s="9"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>45797</v>
       </c>
@@ -18467,7 +18467,7 @@
       </c>
       <c r="I192" s="9"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>45796</v>
       </c>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="I193" s="9"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>45793</v>
       </c>
@@ -18531,7 +18531,7 @@
       </c>
       <c r="I194" s="9"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>45792</v>
       </c>
@@ -18563,7 +18563,7 @@
       </c>
       <c r="I195" s="9"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>45791</v>
       </c>
@@ -18595,7 +18595,7 @@
       </c>
       <c r="I196" s="9"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>45790</v>
       </c>
@@ -18627,7 +18627,7 @@
       </c>
       <c r="I197" s="9"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>45789</v>
       </c>
@@ -18659,7 +18659,7 @@
       </c>
       <c r="I198" s="9"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>45786</v>
       </c>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="I199" s="9"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>45785</v>
       </c>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="I200" s="9"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>45784</v>
       </c>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="I201" s="9"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>45783</v>
       </c>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="I202" s="9"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>45782</v>
       </c>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="I203" s="9"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>45779</v>
       </c>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="I204" s="9"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>45778</v>
       </c>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="I205" s="9"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>45777</v>
       </c>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="I206" s="9"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>45776</v>
       </c>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="I207" s="9"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>45775</v>
       </c>
@@ -18979,7 +18979,7 @@
       </c>
       <c r="I208" s="9"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>45772</v>
       </c>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="I209" s="9"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>45771</v>
       </c>
@@ -19043,7 +19043,7 @@
       </c>
       <c r="I210" s="9"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>45770</v>
       </c>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="I211" s="9"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>45769</v>
       </c>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="I212" s="9"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>45768</v>
       </c>
@@ -19139,7 +19139,7 @@
       </c>
       <c r="I213" s="9"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>45765</v>
       </c>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="I214" s="9"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>45764</v>
       </c>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="I215" s="9"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>45763</v>
       </c>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="I216" s="9"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>45762</v>
       </c>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="I217" s="9"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>45761</v>
       </c>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="I218" s="9"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>45758</v>
       </c>
@@ -19331,7 +19331,7 @@
       </c>
       <c r="I219" s="9"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>45757</v>
       </c>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="I220" s="9"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>45756</v>
       </c>
@@ -19395,7 +19395,7 @@
       </c>
       <c r="I221" s="9"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>45755</v>
       </c>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="I222" s="9"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>45754</v>
       </c>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="I223" s="9"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>45751</v>
       </c>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="I224" s="9"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>45750</v>
       </c>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="I225" s="9"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>45749</v>
       </c>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="I226" s="9"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>45748</v>
       </c>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="I227" s="9"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>45747</v>
       </c>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="I228" s="9"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>45744</v>
       </c>
@@ -19651,7 +19651,7 @@
       </c>
       <c r="I229" s="9"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>45743</v>
       </c>
@@ -19683,7 +19683,7 @@
       </c>
       <c r="I230" s="9"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>45742</v>
       </c>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="I231" s="9"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>45741</v>
       </c>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="I232" s="9"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>45740</v>
       </c>
@@ -19779,7 +19779,7 @@
       </c>
       <c r="I233" s="9"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>45737</v>
       </c>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="I234" s="9"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>45736</v>
       </c>
@@ -19843,7 +19843,7 @@
       </c>
       <c r="I235" s="9"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>45735</v>
       </c>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="I236" s="9"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>45734</v>
       </c>
@@ -19907,7 +19907,7 @@
       </c>
       <c r="I237" s="9"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>45733</v>
       </c>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="I238" s="9"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>45730</v>
       </c>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="I239" s="9"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>45729</v>
       </c>
@@ -20003,7 +20003,7 @@
       </c>
       <c r="I240" s="9"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>45728</v>
       </c>
@@ -20035,7 +20035,7 @@
       </c>
       <c r="I241" s="9"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>45727</v>
       </c>
@@ -20067,7 +20067,7 @@
       </c>
       <c r="I242" s="9"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>45726</v>
       </c>
@@ -20099,7 +20099,7 @@
       </c>
       <c r="I243" s="9"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>45723</v>
       </c>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="I244" s="9"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>45722</v>
       </c>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="I245" s="9"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>45721</v>
       </c>
@@ -20195,7 +20195,7 @@
       </c>
       <c r="I246" s="9"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>45720</v>
       </c>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="I247" s="9"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>45719</v>
       </c>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="I248" s="9"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>45716</v>
       </c>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="I249" s="9"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>45715</v>
       </c>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="I250" s="9"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>45714</v>
       </c>
@@ -20355,7 +20355,7 @@
       </c>
       <c r="I251" s="9"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>45713</v>
       </c>
@@ -20387,7 +20387,7 @@
       </c>
       <c r="I252" s="9"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>45712</v>
       </c>
@@ -20419,7 +20419,7 @@
       </c>
       <c r="I253" s="9"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>45709</v>
       </c>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="I254" s="9"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>45708</v>
       </c>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="I255" s="9"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>45707</v>
       </c>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="I256" s="9"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>45706</v>
       </c>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="I257" s="9"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>45705</v>
       </c>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="I258" s="9"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>45702</v>
       </c>
@@ -20611,7 +20611,7 @@
       </c>
       <c r="I259" s="9"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>45701</v>
       </c>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="I260" s="9"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>45700</v>
       </c>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="I261" s="9"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>45699</v>
       </c>
